--- a/tools/catalogue.xlsx
+++ b/tools/catalogue.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\tax docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\meal plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC328F5-F27E-4691-88E8-70BD124A8D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67B7FFB5-8848-48AD-B0FB-DBAA8D5A6D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,7 +949,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="3">
-        <v>2200</v>
+        <v>2450</v>
       </c>
       <c r="D2" t="s">
         <v>88</v>
@@ -963,7 +963,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>2700</v>
+        <v>2950</v>
       </c>
       <c r="D3" t="s">
         <v>89</v>
@@ -991,7 +991,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="3">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="D5" t="s">
         <v>91</v>
@@ -1005,7 +1005,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="2">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -1047,7 +1047,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="3">
-        <v>3300</v>
+        <v>3950</v>
       </c>
       <c r="D9" t="s">
         <v>95</v>
@@ -1075,7 +1075,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="D11" t="s">
         <v>97</v>
@@ -1173,7 +1173,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="3">
-        <v>1440</v>
+        <v>1600</v>
       </c>
       <c r="D18" t="s">
         <v>104</v>
@@ -1285,7 +1285,7 @@
         <v>39</v>
       </c>
       <c r="C26" s="3">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="D26" t="s">
         <v>112</v>
@@ -1355,7 +1355,7 @@
         <v>44</v>
       </c>
       <c r="C31" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D31" t="s">
         <v>117</v>
@@ -1411,7 +1411,7 @@
         <v>48</v>
       </c>
       <c r="C35">
-        <v>1950</v>
+        <v>900</v>
       </c>
       <c r="D35" t="s">
         <v>121</v>
@@ -1425,7 +1425,7 @@
         <v>49</v>
       </c>
       <c r="C36">
-        <v>900</v>
+        <v>2100</v>
       </c>
       <c r="D36" t="s">
         <v>122</v>
@@ -1439,7 +1439,7 @@
         <v>50</v>
       </c>
       <c r="C37" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="D37" t="s">
         <v>123</v>
@@ -1467,7 +1467,7 @@
         <v>52</v>
       </c>
       <c r="C39" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="D39" t="s">
         <v>125</v>
@@ -1481,7 +1481,7 @@
         <v>53</v>
       </c>
       <c r="C40" s="3">
-        <v>1950</v>
+        <v>2200</v>
       </c>
       <c r="D40" t="s">
         <v>126</v>
@@ -1495,7 +1495,7 @@
         <v>54</v>
       </c>
       <c r="C41" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="D41" t="s">
         <v>127</v>
@@ -1523,7 +1523,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="3">
-        <v>1440</v>
+        <v>1600</v>
       </c>
       <c r="D43" t="s">
         <v>104</v>
@@ -1691,7 +1691,7 @@
         <v>65</v>
       </c>
       <c r="C55">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D55" t="s">
         <v>140</v>
@@ -1733,7 +1733,7 @@
         <v>68</v>
       </c>
       <c r="C58">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D58" t="s">
         <v>143</v>
@@ -1775,7 +1775,7 @@
         <v>71</v>
       </c>
       <c r="C61">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="D61" t="s">
         <v>146</v>
@@ -1901,7 +1901,7 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="D70" t="s">
         <v>155</v>

--- a/tools/catalogue.xlsx
+++ b/tools/catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\meal plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67B7FFB5-8848-48AD-B0FB-DBAA8D5A6D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5D7E1C-7781-455F-B2EE-96088E5077F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="159">
   <si>
     <t>Collection</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Keto Drinks</t>
   </si>
   <si>
-    <t>Ramadan Special</t>
-  </si>
-  <si>
     <t>Keto Brownies (pack of 6)</t>
   </si>
   <si>
@@ -285,12 +282,6 @@
     <t>Keto Salted Lemon Fizz (475ml)</t>
   </si>
   <si>
-    <t>Keto Chicken Cheese Balls (pack of 6)</t>
-  </si>
-  <si>
-    <t>Keto Mozzarella Cheese Sticks (pack of 5)</t>
-  </si>
-  <si>
     <t>Premium almond flour and allulose; macros per square: Fat 19.5g, Protein 3.1g, Carbs 2.3g, Energy 198kcal</t>
   </si>
   <si>
@@ -511,12 +502,6 @@
   </si>
   <si>
     <t>Electrolyte drink made with Himalayan pink salt (500mg sodium), Losalt (600mg potassium), lemon juice and mineral water; hydrating and sugar-free; macros not provided.</t>
-  </si>
-  <si>
-    <t>Hidden item; tender chicken balls stuffed with melted mozzarella cheese and coated in a keto-friendly exterior; perfect balance of protein and healthy fats; macros not provided.</t>
-  </si>
-  <si>
-    <t>Hidden item; generous mozzarella cheese coated in crispy keto-friendly breading; only a few grams of net carbs per serving; macros not provided.</t>
   </si>
 </sst>
 </file>
@@ -920,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -946,13 +931,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3">
         <v>2450</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,13 +945,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3">
         <v>2950</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -974,13 +959,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3">
         <v>2500</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -988,13 +973,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>1450</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,13 +987,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2">
         <v>800</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1016,13 +1001,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3">
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1030,13 +1015,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <v>5600</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1044,13 +1029,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3">
         <v>3950</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1058,13 +1043,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3">
         <v>5200</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1072,13 +1057,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3">
         <v>2500</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,13 +1071,13 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3">
         <v>1900</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,13 +1085,13 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3">
         <v>5200</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1114,13 +1099,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3">
         <v>1600</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,13 +1113,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3">
         <v>4900</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1142,13 +1127,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3">
         <v>5200</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,13 +1141,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2">
         <v>850</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1170,13 +1155,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3">
         <v>1600</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1184,13 +1169,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3">
         <v>4600</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,13 +1183,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3">
         <v>2500</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1212,13 +1197,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3">
         <v>1900</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1226,13 +1211,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3">
         <v>2000</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,13 +1225,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3">
         <v>3500</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2">
         <v>450</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,13 +1253,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2">
         <v>550</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3">
         <v>3000</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,13 +1281,13 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2">
         <v>950</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,13 +1295,13 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="3">
         <v>1950</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1324,13 +1309,13 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2">
         <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1338,13 +1323,13 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2">
         <v>900</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1352,13 +1337,13 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2">
         <v>800</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1366,13 +1351,13 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3">
         <v>1150</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,13 +1365,13 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33">
         <v>2100</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,13 +1379,13 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34">
         <v>1950</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1408,13 +1393,13 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35">
         <v>900</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,13 +1407,13 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36">
         <v>2100</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,13 +1421,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3">
         <v>3200</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,13 +1435,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="3">
         <v>1950</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,13 +1449,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="3">
         <v>2800</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,13 +1463,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="3">
         <v>2200</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,13 +1477,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3">
         <v>3100</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,13 +1491,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" s="3">
         <v>2700</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,13 +1505,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="3">
         <v>1600</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,13 +1519,13 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44">
         <v>1600</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,13 +1533,13 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45">
         <v>1900</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,13 +1547,13 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C46">
         <v>1900</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,13 +1561,13 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47">
         <v>1700</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,13 +1575,13 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48">
         <v>700</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,13 +1589,13 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49">
         <v>1600</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,13 +1603,13 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C50">
         <v>2500</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,13 +1617,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1100</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,13 +1631,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52">
         <v>2800</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,13 +1645,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53">
         <v>2200</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,13 +1659,13 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>3100</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,13 +1673,13 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>2250</v>
       </c>
       <c r="D55" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1702,13 +1687,13 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56">
         <v>5250</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,13 +1701,13 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57">
         <v>3250</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,13 +1715,13 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58">
         <v>2250</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,13 +1729,13 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59">
         <v>1600</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,13 +1743,13 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60">
         <v>999</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,13 +1757,13 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61">
         <v>4800</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1786,13 +1771,13 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>7200</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,13 +1785,13 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63">
         <v>4000</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,13 +1799,13 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64">
         <v>2300</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,13 +1813,13 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>1250</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>1500</v>
       </c>
       <c r="D66" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1856,13 +1841,13 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67">
         <v>1400</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,13 +1855,13 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68">
         <v>2650</v>
       </c>
       <c r="D68" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,13 +1869,13 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C69">
         <v>2100</v>
       </c>
       <c r="D69" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,13 +1883,13 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C70">
         <v>1400</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1912,13 +1897,13 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C71">
         <v>2800</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,13 +1911,13 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C72">
         <v>1500</v>
       </c>
       <c r="D72" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1940,13 +1925,13 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C73">
         <v>2200</v>
       </c>
       <c r="D73" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1954,13 +1939,13 @@
         <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C74">
         <v>175</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,13 +1953,13 @@
         <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75">
         <v>500</v>
       </c>
       <c r="D75" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1982,41 +1967,13 @@
         <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C76">
         <v>400</v>
       </c>
       <c r="D76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77">
-        <v>900</v>
-      </c>
-      <c r="D77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78">
-        <v>950</v>
-      </c>
-      <c r="D78" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/tools/catalogue.xlsx
+++ b/tools/catalogue.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\meal plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5D7E1C-7781-455F-B2EE-96088E5077F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C861C4-58DA-432C-854F-ACE9DB1E9198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="142">
   <si>
     <t>Collection</t>
   </si>
@@ -114,9 +117,6 @@
     <t>Peanut butter Keto Icecream (1ltr)</t>
   </si>
   <si>
-    <t>Keto Sundae (Death by Chocolate)</t>
-  </si>
-  <si>
     <t>Keto Zera Biscuits (12pcs)</t>
   </si>
   <si>
@@ -162,9 +162,6 @@
     <t>Keto Double Cheese Melt</t>
   </si>
   <si>
-    <t>Keto Pizza (7 inches diameter)</t>
-  </si>
-  <si>
     <t>Baked Chicken with cheese</t>
   </si>
   <si>
@@ -177,9 +174,6 @@
     <t>Keto Blanched Almond Flour Bread (loaf)</t>
   </si>
   <si>
-    <t>Keto Coconut Flour Buns (pack of 5)</t>
-  </si>
-  <si>
     <t>Keto Raw Almond Flour Bread</t>
   </si>
   <si>
@@ -243,18 +237,9 @@
     <t>Blanched Almond Flour (super fine imported) (1kg)</t>
   </si>
   <si>
-    <t>Monkfruit Stevia Blend (1kg)</t>
-  </si>
-  <si>
-    <t>Monkfruit Stevia Blend (500gm)</t>
-  </si>
-  <si>
     <t>Liquid Monkfruit (15ml)</t>
   </si>
   <si>
-    <t>Keto Chicken Fettuccini Pasta with Alfredo Sauce (Half box, 300g)</t>
-  </si>
-  <si>
     <t>Keto Lasagna Sheets (Raw)</t>
   </si>
   <si>
@@ -264,9 +249,6 @@
     <t>Keto Fettuccini Pasta (Raw)</t>
   </si>
   <si>
-    <t>Keto Lasagne (2-3 persons)</t>
-  </si>
-  <si>
     <t>Keto Egg Noodles / Chowmein (250gm raw)</t>
   </si>
   <si>
@@ -327,9 +309,6 @@
     <t>Sugar-free peanut butter ice cream made with keto-friendly ingredients; macros not provided</t>
   </si>
   <si>
-    <t>Triple-layered chocolate cake topped with silky chocolate sauce; macros per cup: Fats 14.9g, Protein 4.5g, Carbs &lt;5g, Energy 177.8kcal</t>
-  </si>
-  <si>
     <t>Zeera biscuits made with almond flour and monkfruit sweetener; macros per piece: Energy 53.15kcal, Fat 4.97g, Protein 1.47g, Carbs 0.63g</t>
   </si>
   <si>
@@ -375,9 +354,6 @@
     <t>Double cheese burger served with keto sauce; macros per half burger: Fat 54.8g, Protein 40.8g, Carbs 5g, Energy 676kcal</t>
   </si>
   <si>
-    <t>Personal-size keto pizza; macros per slice: Fat 26.1g, Protein 26.6g, Carbs 1.8g, Energy 345kcal</t>
-  </si>
-  <si>
     <t>Oven‑baked chicken topped with cheese; macros per box: Fat 37.6g, Protein 46.1g, Carbs 2.1g, Energy 531.5kcal</t>
   </si>
   <si>
@@ -390,9 +366,6 @@
     <t>Fine blanched almond flour bread with butter and eggs; macros per slice: Fat 18.5g, Protein 7g, Carbs 2.5g, Energy 204kcal</t>
   </si>
   <si>
-    <t>Soft buns made with coconut flour; macros per bun: Fat 21.2g, Protein 2.38g, Carbs 3.06g, Energy 212.56kcal</t>
-  </si>
-  <si>
     <t>Bread made with raw almond flour; macros per slice: Fat 25.7g, Protein 7g, Carbs 2.4g, Energy 269kcal</t>
   </si>
   <si>
@@ -411,9 +384,6 @@
     <t>Fresh farm-picked tomatoes, allulose sweetener and no preservatives; macros per tbsp: fat 0.04g, protein 0.52g, carbs 1.6g, energy 9kcal.</t>
   </si>
   <si>
-    <t>Rich heavy cream and allulose sweetener; macros per tablespoon: fat 3.7g, protein 0.2g, carbs 0.2g, energy 35kcal.</t>
-  </si>
-  <si>
     <t>High-omega-3 eggs, allulose and red pepper; macros per tablespoon: fat 10.3g, protein 0.51g, carbs 0.1g, energy 94.8kcal.</t>
   </si>
   <si>
@@ -423,9 +393,6 @@
     <t>Keto-friendly sweet chili sauce made with sugar-free ingredients; macros not provided.</t>
   </si>
   <si>
-    <t>Rich and silky dark chocolate spread sweetened with allulose; suitable for diabetics and kids.</t>
-  </si>
-  <si>
     <t>Concentrated chatni made with mint and garlic; mix 1 tbsp with Greek yogurt and chaat masala for serving; macros not provided.</t>
   </si>
   <si>
@@ -462,31 +429,16 @@
     <t>Super fine blanched almond flour imported from renowned mills; perfect for baking; macros not provided.</t>
   </si>
   <si>
-    <t>Non-GMO, Halal-certified sweetener blend; 50% less bitter than local stevia; economical; only 2g needed to sweeten a cup; macros not provided.</t>
-  </si>
-  <si>
-    <t>Smaller pack of the monkfruit stevia blend; same benefits as the 1kg pack; macros not provided.</t>
-  </si>
-  <si>
     <t>Pure monkfruit liquid extract for sweetening beverages; macros not provided.</t>
   </si>
   <si>
-    <t>Zero-carb keto pasta smothered in creamy Alfredo sauce with garlic, parsley and parmesan; macros per serving: fats 30g, protein 10g, carbs 2g, energy 318kcal.</t>
-  </si>
-  <si>
     <t>Egg-based keto-friendly lasagna sheets; mimic taste and texture of traditional pasta; ready to use; macros not provided.</t>
   </si>
   <si>
     <t>Full box of zero-carb pasta with creamy Alfredo sauce; macros per half box: fats 30g, protein 10g, carbs 2g, energy 318kcal.</t>
   </si>
   <si>
-    <t>Juicy chicken, melted cheese, herbs and condiments on a coconut-flour crust; macros per slice: fat 26.1g, protein 26.6g, carbs 1.8g, energy 345kcal.</t>
-  </si>
-  <si>
     <t>Raw keto-friendly fettuccini pasta made from eggs and keto flours; ready to use; macros not provided.</t>
-  </si>
-  <si>
-    <t>Low-carb twist on classic lasagna with zero-carb sheets, ground beef and keto sauces; macros per box: carbs 7g, protein 65g, fats 70g, total calories 918kcal.</t>
   </si>
   <si>
     <t>Zero-carb raw keto chowmein made from real eggs; no preservatives; macros per 300g: energy 48.5kcal, fats 4.1g, proteins 2.4g, carbs 0.5g.</t>
@@ -571,7 +523,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -905,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -937,7 +900,7 @@
         <v>2450</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -951,7 +914,7 @@
         <v>2950</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -965,7 +928,7 @@
         <v>2500</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -979,7 +942,7 @@
         <v>1450</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,7 +956,7 @@
         <v>800</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1007,7 +970,7 @@
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,7 +984,7 @@
         <v>5600</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,7 +998,7 @@
         <v>3950</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,7 +1012,7 @@
         <v>5200</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,7 +1026,7 @@
         <v>2500</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,7 +1040,7 @@
         <v>1900</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,7 +1054,7 @@
         <v>5200</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,7 +1068,7 @@
         <v>1600</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1082,7 @@
         <v>4900</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,7 +1096,7 @@
         <v>5200</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1143,11 +1106,11 @@
       <c r="B17" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="2">
-        <v>850</v>
+      <c r="C17" s="3">
+        <v>1600</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,10 +1121,10 @@
         <v>30</v>
       </c>
       <c r="C18" s="3">
-        <v>1600</v>
+        <v>4600</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1172,10 +1135,10 @@
         <v>31</v>
       </c>
       <c r="C19" s="3">
-        <v>4600</v>
+        <v>2500</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1186,10 +1149,10 @@
         <v>32</v>
       </c>
       <c r="C20" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,10 +1163,10 @@
         <v>33</v>
       </c>
       <c r="C21" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,10 +1177,10 @@
         <v>34</v>
       </c>
       <c r="C22" s="3">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,11 +1190,11 @@
       <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="3">
-        <v>3500</v>
+      <c r="C23" s="2">
+        <v>450</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,10 +1205,10 @@
         <v>36</v>
       </c>
       <c r="C24" s="2">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,25 +1218,25 @@
       <c r="B25" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="2">
-        <v>550</v>
+      <c r="C25" s="3">
+        <v>3000</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="3">
-        <v>3000</v>
+      <c r="C26" s="2">
+        <v>950</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,11 +1246,11 @@
       <c r="B27" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="2">
-        <v>950</v>
+      <c r="C27" s="3">
+        <v>1950</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,11 +1260,11 @@
       <c r="B28" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="3">
-        <v>1950</v>
+      <c r="C28" s="2">
+        <v>600</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,10 +1275,10 @@
         <v>41</v>
       </c>
       <c r="C29" s="2">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1289,10 @@
         <v>42</v>
       </c>
       <c r="C30" s="2">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,11 +1302,11 @@
       <c r="B31" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="2">
-        <v>800</v>
+      <c r="C31" s="3">
+        <v>1150</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,11 +1316,11 @@
       <c r="B32" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="3">
-        <v>1150</v>
+      <c r="C32">
+        <v>1950</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1331,10 @@
         <v>45</v>
       </c>
       <c r="C33">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,38 +1345,38 @@
         <v>46</v>
       </c>
       <c r="C34">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
       </c>
-      <c r="C35">
-        <v>900</v>
+      <c r="C35" s="3">
+        <v>3200</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36">
-        <v>2100</v>
+      <c r="C36" s="3">
+        <v>2800</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,10 +1387,10 @@
         <v>49</v>
       </c>
       <c r="C37" s="3">
-        <v>3200</v>
+        <v>2200</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,10 +1401,10 @@
         <v>50</v>
       </c>
       <c r="C38" s="3">
-        <v>1950</v>
+        <v>3100</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,66 +1415,66 @@
         <v>51</v>
       </c>
       <c r="C39" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="3">
-        <v>2200</v>
+      <c r="C40">
+        <v>1600</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="3">
-        <v>3100</v>
+      <c r="C41">
+        <v>1900</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="3">
-        <v>2700</v>
+      <c r="C42">
+        <v>1700</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="3">
-        <v>1600</v>
+        <v>55</v>
+      </c>
+      <c r="C43">
+        <v>700</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,13 +1482,13 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44">
         <v>1600</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,13 +1496,13 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,13 +1510,13 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C46">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,422 +1524,272 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C47">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="D47" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C48">
-        <v>700</v>
+        <v>3100</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C49">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D49" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C50">
-        <v>2500</v>
+        <v>5250</v>
       </c>
       <c r="D50" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C51">
-        <v>1100</v>
+        <v>3250</v>
       </c>
       <c r="D51" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C52">
-        <v>2800</v>
+        <v>2250</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C53">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C54">
-        <v>3100</v>
+        <v>999</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C55">
-        <v>2250</v>
+        <v>4800</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C56">
-        <v>5250</v>
+        <v>7200</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C57">
-        <v>3250</v>
+        <v>1250</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C58">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="D58" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C59">
-        <v>1600</v>
+        <v>2650</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C60">
-        <v>999</v>
+        <v>1400</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C61">
-        <v>4800</v>
+        <v>1500</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C62">
-        <v>7200</v>
+        <v>2200</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C63">
-        <v>4000</v>
+        <v>175</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C64">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="D64" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C65">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="D65" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66">
-        <v>1500</v>
-      </c>
-      <c r="D66" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" t="s">
-        <v>76</v>
-      </c>
-      <c r="C67">
-        <v>1400</v>
-      </c>
-      <c r="D67" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68">
-        <v>2650</v>
-      </c>
-      <c r="D68" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69">
-        <v>2100</v>
-      </c>
-      <c r="D69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70">
-        <v>1400</v>
-      </c>
-      <c r="D70" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71">
-        <v>2800</v>
-      </c>
-      <c r="D71" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72">
-        <v>1500</v>
-      </c>
-      <c r="D72" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73">
-        <v>2200</v>
-      </c>
-      <c r="D73" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74">
-        <v>175</v>
-      </c>
-      <c r="D74" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75">
-        <v>500</v>
-      </c>
-      <c r="D75" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76">
-        <v>400</v>
-      </c>
-      <c r="D76" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>